--- a/StructureDefinition-ophthalmic-humphrey-visual-field.xlsx
+++ b/StructureDefinition-ophthalmic-humphrey-visual-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T00:41:24+00:00</t>
+    <t>2026-08-25T02:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-humphrey-visual-field.xlsx
+++ b/StructureDefinition-ophthalmic-humphrey-visual-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T02:25:39+00:00</t>
+    <t>2026-08-25T18:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-humphrey-visual-field.xlsx
+++ b/StructureDefinition-ophthalmic-humphrey-visual-field.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T18:52:20+00:00</t>
+    <t>2026-09-01T17:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -757,7 +757,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ophthalmic-encounter)
 </t>
   </si>
   <si>
@@ -1259,7 +1259,7 @@
 </t>
   </si>
   <si>
-    <t>(Measurement) Device</t>
+    <t>Acquisition device (manufacturer, model, software version)</t>
   </si>
   <si>
     <t>The device used to generate the observation data.</t>
@@ -1737,7 +1737,7 @@
     <t>Observation.component:screeningMode.code</t>
   </si>
   <si>
-    <t>DICOM CID 4252</t>
+    <t>Screening test mode - type of screening test. DICOM CID 4252</t>
   </si>
   <si>
     <t>Observation.component:screeningMode.value[x]</t>
@@ -1770,7 +1770,7 @@
     <t>Observation.component:fixationStrategy.code</t>
   </si>
   <si>
-    <t>DICOM CID 4253</t>
+    <t>Fixation strategy - how fixation was monitored. DICOM CID 4253</t>
   </si>
   <si>
     <t>Observation.component:fixationStrategy.value[x]</t>
@@ -1803,7 +1803,7 @@
     <t>Observation.component:stimulusSize.code</t>
   </si>
   <si>
-    <t>DICOM (0024,0025)</t>
+    <t>Stimulus size - Goldmann stimulus size used, usually Goldmann III. DICOM (0024,0025)</t>
   </si>
   <si>
     <t>Observation.component:stimulusSize.value[x]</t>
@@ -1836,7 +1836,7 @@
     <t>Observation.component:stimulusColor.code</t>
   </si>
   <si>
-    <t>DICOM CID 4255 / (0024,0021)</t>
+    <t>Stimulus color - color of stimulus light. DICOM CID 4255 / (0024,0021)</t>
   </si>
   <si>
     <t>Observation.component:stimulusColor.value[x]</t>
@@ -1869,7 +1869,7 @@
     <t>Observation.component:bgLuminance.code</t>
   </si>
   <si>
-    <t>DICOM (0024,0020)</t>
+    <t>Background luminance - background bowl luminance, standard 31.5 asb. DICOM (0024,0020)</t>
   </si>
   <si>
     <t>Observation.component:bgLuminance.value[x]</t>
@@ -1902,7 +1902,7 @@
     <t>Observation.component:maxLuminance.code</t>
   </si>
   <si>
-    <t>DICOM (0024,0018)</t>
+    <t>Maximum stimulus luminance - maximum stimulus intensity. DICOM (0024,0018)</t>
   </si>
   <si>
     <t>Observation.component:maxLuminance.value[x]</t>
@@ -1935,7 +1935,7 @@
     <t>Observation.component:stimulusDuration.code</t>
   </si>
   <si>
-    <t>DICOM (0024,0028)</t>
+    <t>Stimulus duration - presentation time, standard 200ms. DICOM (0024,0028)</t>
   </si>
   <si>
     <t>Observation.component:stimulusDuration.value[x]</t>
@@ -1968,7 +1968,7 @@
     <t>Observation.component:hExtent.code</t>
   </si>
   <si>
-    <t>DICOM (0024,0010)</t>
+    <t>Visual field horizontal extent - horizontal extent of tested field. DICOM (0024,0010)</t>
   </si>
   <si>
     <t>Observation.component:hExtent.value[x]</t>
@@ -2001,7 +2001,7 @@
     <t>Observation.component:vExtent.code</t>
   </si>
   <si>
-    <t>DICOM (0024,0011)</t>
+    <t>Visual field vertical extent - vertical extent of tested field. DICOM (0024,0011)</t>
   </si>
   <si>
     <t>Observation.component:vExtent.value[x]</t>
@@ -2034,7 +2034,7 @@
     <t>Observation.component:fieldShape.code</t>
   </si>
   <si>
-    <t>DICOM (0024,0012)</t>
+    <t>Visual field shape - shape of tested field (circle or rectangle). DICOM (0024,0012)</t>
   </si>
   <si>
     <t>Observation.component:fieldShape.value[x]</t>
@@ -2166,7 +2166,7 @@
     <t>Observation.component:correctionLens.code</t>
   </si>
   <si>
-    <t>DICOM CID 4256, Procedure Modifier</t>
+    <t>Correction lens used - whether correction lens was used during test. DICOM CID 4256, Procedure Modifier</t>
   </si>
   <si>
     <t>Observation.component:correctionLens.value[x]</t>
@@ -4758,7 +4758,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>233</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>83</v>
@@ -4880,7 +4880,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>244</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>83</v>
@@ -7168,7 +7168,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>394</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>83</v>
